--- a/Grafico_Grupo de Despesa.xlsx
+++ b/Grafico_Grupo de Despesa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Rei-1cpd003\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\172.17.1.6\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392F83E7-D7BC-4DC4-94CE-5A14720FE1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE81928D-6797-43A5-B84C-C80579807901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
   </bookViews>
   <sheets>
     <sheet name="ReceitaXDespesa" sheetId="3" r:id="rId1"/>
@@ -128,9 +128,6 @@
     <t>*Atualizado até Julho/2026 (Em 31/07/2026).</t>
   </si>
   <si>
-    <t>Valor</t>
-  </si>
-  <si>
     <t>Percentual de Receita Arrecadada (B) % (B/A)</t>
   </si>
   <si>
@@ -150,6 +147,9 @@
   </si>
   <si>
     <t>Item Orçamentário</t>
+  </si>
+  <si>
+    <t>Valor (Em milhões)</t>
   </si>
 </sst>
 </file>
@@ -334,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -406,8 +406,19 @@
     <xf numFmtId="4" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2701,61 +2712,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20333736-63C4-4805-88B4-CD691F856C39}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="31" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="28" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="27">
+      <c r="A2" s="30">
         <v>46023</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1">
-        <v>84416666.666666672</v>
+      <c r="C2" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="27">
+      <c r="A3" s="30">
         <v>46023</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="1">
-        <v>62844099.030000001</v>
+        <f>62844099.03/1000000</f>
+        <v>62.844099030000002</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
+      <c r="A4" s="30">
         <v>46023</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="1">
-        <v>154635427.19999999</v>
+        <f>154635427.2/1000000</f>
+        <v>154.63542719999998</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
+      <c r="A5" s="30">
         <v>46023</v>
       </c>
       <c r="B5" t="s">
@@ -2763,44 +2777,47 @@
       </c>
       <c r="C5" s="1">
         <f>C3-C4</f>
-        <v>-91791328.169999987</v>
+        <v>-91.791328169999986</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
+      <c r="A6" s="30">
         <v>46054</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="1">
-        <v>84416666.666666672</v>
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="30">
         <v>46054</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="1">
-        <v>71107409.859999999</v>
+        <f>71107409.86/1000000</f>
+        <v>71.107409860000004</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
+      <c r="A8" s="30">
         <v>46054</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="1">
-        <v>65867006.619999997</v>
+        <f>65867006.62/1000000</f>
+        <v>65.867006619999998</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
+      <c r="A9" s="30">
         <v>46054</v>
       </c>
       <c r="B9" t="s">
@@ -2808,44 +2825,47 @@
       </c>
       <c r="C9" s="1">
         <f>C7-C8</f>
-        <v>5240403.2400000021</v>
+        <v>5.2404032400000062</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
+      <c r="A10" s="30">
         <v>46082</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="1">
-        <v>84416666.666666672</v>
+      <c r="C10" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
+      <c r="A11" s="30">
         <v>46082</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="1">
-        <v>75044984.989999995</v>
+        <f>75044984.99/1000000</f>
+        <v>75.044984989999989</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="27">
+      <c r="A12" s="30">
         <v>46082</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="1">
-        <v>54581181.280000001</v>
+        <f>54581181.28/1000000</f>
+        <v>54.581181280000003</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="27">
+      <c r="A13" s="30">
         <v>46082</v>
       </c>
       <c r="B13" t="s">
@@ -2853,44 +2873,47 @@
       </c>
       <c r="C13" s="1">
         <f>C11-C12</f>
-        <v>20463803.709999993</v>
+        <v>20.463803709999986</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
+      <c r="A14" s="30">
         <v>46113</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1">
-        <v>84416666.666666672</v>
+      <c r="C14" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
+      <c r="A15" s="30">
         <v>46113</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="1">
-        <v>91828183.739999995</v>
+        <f>91828183.74/1000000</f>
+        <v>91.82818374</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="27">
+      <c r="A16" s="30">
         <v>46113</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="1">
-        <v>41371067.399999999</v>
+        <f>41371067.4/1000000</f>
+        <v>41.371067400000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="27">
+      <c r="A17" s="30">
         <v>46113</v>
       </c>
       <c r="B17" t="s">
@@ -2898,44 +2921,47 @@
       </c>
       <c r="C17" s="1">
         <f>C15-C16</f>
-        <v>50457116.339999996</v>
+        <v>50.457116339999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
+      <c r="A18" s="30">
         <v>46143</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="1">
-        <v>84416666.666666672</v>
+      <c r="C18" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="27">
+      <c r="A19" s="30">
         <v>46143</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="1">
-        <v>77415932.5</v>
+        <f>77415932.5/1000000</f>
+        <v>77.415932499999997</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="27">
+      <c r="A20" s="30">
         <v>46143</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="1">
-        <v>80184171.170000002</v>
+        <f>80184171.17/1000000</f>
+        <v>80.184171169999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="27">
+      <c r="A21" s="30">
         <v>46143</v>
       </c>
       <c r="B21" t="s">
@@ -2943,44 +2969,47 @@
       </c>
       <c r="C21" s="1">
         <f>C19-C20</f>
-        <v>-2768238.6700000018</v>
+        <v>-2.7682386700000023</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="27">
+      <c r="A22" s="30">
         <v>46174</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="1">
-        <v>84416666.666666672</v>
+      <c r="C22" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="30">
         <v>46174</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
       </c>
       <c r="C23" s="1">
-        <v>75166762.640000001</v>
+        <f>75166762.64/1000000</f>
+        <v>75.166762640000002</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="27">
+      <c r="A24" s="30">
         <v>46174</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="1">
-        <v>92382151.069999993</v>
+        <f>92382151.07/1000000</f>
+        <v>92.382151069999992</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+      <c r="A25" s="30">
         <v>46174</v>
       </c>
       <c r="B25" t="s">
@@ -2988,44 +3017,47 @@
       </c>
       <c r="C25" s="1">
         <f>C23-C24</f>
-        <v>-17215388.429999992</v>
+        <v>-17.21538842999999</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="27">
+      <c r="A26" s="30">
         <v>46204</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="1">
-        <v>84416666.666666672</v>
+      <c r="C26" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="27">
+      <c r="A27" s="30">
         <v>46204</v>
       </c>
       <c r="B27" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="1">
-        <v>70888043.189999998</v>
+        <f>70888043.19/1000000</f>
+        <v>70.888043189999991</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="27">
+      <c r="A28" s="30">
         <v>46204</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
       <c r="C28" s="1">
-        <v>99462564.390000001</v>
+        <f>99462564.39/1000000</f>
+        <v>99.462564389999997</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
+      <c r="A29" s="30">
         <v>46204</v>
       </c>
       <c r="B29" t="s">
@@ -3033,22 +3065,23 @@
       </c>
       <c r="C29" s="1">
         <f>C27-C28</f>
-        <v>-28574521.200000003</v>
+        <v>-28.574521200000007</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
+      <c r="A30" s="30">
         <v>46235</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="1">
-        <v>84416666.666666672</v>
+      <c r="C30" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
+      <c r="A31" s="30">
         <v>46235</v>
       </c>
       <c r="B31" t="s">
@@ -3057,7 +3090,7 @@
       <c r="C31" s="1"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
+      <c r="A32" s="30">
         <v>46235</v>
       </c>
       <c r="B32" t="s">
@@ -3066,7 +3099,7 @@
       <c r="C32" s="1"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="27">
+      <c r="A33" s="30">
         <v>46235</v>
       </c>
       <c r="B33" t="s">
@@ -3078,18 +3111,19 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="27">
+      <c r="A34" s="30">
         <v>46266</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="1">
-        <v>84416666.666666672</v>
+      <c r="C34" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="27">
+      <c r="A35" s="30">
         <v>46266</v>
       </c>
       <c r="B35" t="s">
@@ -3098,7 +3132,7 @@
       <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="27">
+      <c r="A36" s="30">
         <v>46266</v>
       </c>
       <c r="B36" t="s">
@@ -3107,7 +3141,7 @@
       <c r="C36" s="1"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="27">
+      <c r="A37" s="30">
         <v>46266</v>
       </c>
       <c r="B37" t="s">
@@ -3119,18 +3153,19 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="27">
+      <c r="A38" s="30">
         <v>46296</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="1">
-        <v>84416666.666666672</v>
+      <c r="C38" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="27">
+      <c r="A39" s="30">
         <v>46296</v>
       </c>
       <c r="B39" t="s">
@@ -3139,7 +3174,7 @@
       <c r="C39" s="1"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="27">
+      <c r="A40" s="30">
         <v>46296</v>
       </c>
       <c r="B40" t="s">
@@ -3148,7 +3183,7 @@
       <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="27">
+      <c r="A41" s="30">
         <v>46296</v>
       </c>
       <c r="B41" t="s">
@@ -3160,18 +3195,19 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="27">
+      <c r="A42" s="30">
         <v>46327</v>
       </c>
       <c r="B42" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="1">
-        <v>84416666.666666672</v>
+      <c r="C42" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="27">
+      <c r="A43" s="30">
         <v>46327</v>
       </c>
       <c r="B43" t="s">
@@ -3180,7 +3216,7 @@
       <c r="C43" s="1"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="27">
+      <c r="A44" s="30">
         <v>46327</v>
       </c>
       <c r="B44" t="s">
@@ -3189,7 +3225,7 @@
       <c r="C44" s="1"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="27">
+      <c r="A45" s="30">
         <v>46327</v>
       </c>
       <c r="B45" t="s">
@@ -3201,18 +3237,19 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="27">
+      <c r="A46" s="30">
         <v>46357</v>
       </c>
       <c r="B46" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="1">
-        <v>84416666.666666672</v>
+      <c r="C46" s="28">
+        <f>84416666.6666667/1000000</f>
+        <v>84.4166666666667</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="27">
+      <c r="A47" s="30">
         <v>46357</v>
       </c>
       <c r="B47" t="s">
@@ -3221,7 +3258,7 @@
       <c r="C47" s="1"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="27">
+      <c r="A48" s="30">
         <v>46357</v>
       </c>
       <c r="B48" t="s">
@@ -3230,7 +3267,7 @@
       <c r="C48" s="1"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="27">
+      <c r="A49" s="30">
         <v>46357</v>
       </c>
       <c r="B49" t="s">
@@ -3240,6 +3277,18 @@
         <f>C47-C48</f>
         <v>0</v>
       </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="1"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="1"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="1"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3962,7 +4011,7 @@
   <sheetData>
     <row r="2" spans="1:17" s="3" customFormat="1" ht="33.75" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="3" customFormat="1" ht="26.25" x14ac:dyDescent="0.3">
@@ -4127,7 +4176,7 @@
     </row>
     <row r="8" spans="1:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="17">
         <v>154635427.19999999</v>
@@ -4165,7 +4214,7 @@
     </row>
     <row r="9" spans="1:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="9">
         <f>B7-B8</f>
@@ -4225,7 +4274,7 @@
     </row>
     <row r="10" spans="1:17" s="12" customFormat="1" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="20">
         <f t="shared" ref="B10:M10" si="2">B7/B6</f>
@@ -4461,7 +4510,7 @@
     </row>
     <row r="14" spans="1:17" s="12" customFormat="1" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="20">
         <f>B8/N6</f>
@@ -4520,7 +4569,7 @@
     </row>
     <row r="15" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
@@ -4566,7 +4615,7 @@
     </row>
     <row r="58" spans="1:1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/Grafico_Grupo de Despesa.xlsx
+++ b/Grafico_Grupo de Despesa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\172.17.1.6\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Rei-1cpd003\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE81928D-6797-43A5-B84C-C80579807901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC87BE7C-9EAA-4EE5-BC80-06A5EB200220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
   </bookViews>
   <sheets>
     <sheet name="ReceitaXDespesa" sheetId="3" r:id="rId1"/>
@@ -149,7 +149,7 @@
     <t>Item Orçamentário</t>
   </si>
   <si>
-    <t>Valor (Em milhões)</t>
+    <t>Valor</t>
   </si>
 </sst>
 </file>

--- a/Grafico_Grupo de Despesa.xlsx
+++ b/Grafico_Grupo de Despesa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Rei-1cpd003\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC87BE7C-9EAA-4EE5-BC80-06A5EB200220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1313F9-7EF9-4109-9202-884DDAB29182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
   </bookViews>

--- a/Grafico_Grupo de Despesa.xlsx
+++ b/Grafico_Grupo de Despesa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Rei-1cpd003\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\172.17.1.6\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1313F9-7EF9-4109-9202-884DDAB29182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EE4AFB-2C4E-4882-97D3-728CA60F74CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
   </bookViews>
   <sheets>
     <sheet name="ReceitaXDespesa" sheetId="3" r:id="rId1"/>
@@ -3087,7 +3087,10 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="1">
+        <f>76738591.33/1000000</f>
+        <v>76.738591329999991</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="30">
@@ -3096,7 +3099,10 @@
       <c r="B32" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1">
+        <f>77352921.92/1000000</f>
+        <v>77.35292192</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="30">
@@ -3107,7 +3113,7 @@
       </c>
       <c r="C33" s="1">
         <f>C31-C32</f>
-        <v>0</v>
+        <v>-0.61433059000000867</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">

--- a/Grafico_Grupo de Despesa.xlsx
+++ b/Grafico_Grupo de Despesa.xlsx
@@ -2,25 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\172.17.1.6\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Rei-1cpd003\coord_plan_institucional\DADOS CPI\Orçamento\2026\EXECUÇÃO ORÇAMENTÁRIA\RELEXORC_CSV\Saida_PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EE4AFB-2C4E-4882-97D3-728CA60F74CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8707B50-AA76-4BE6-B411-F71B4AF47C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BD803231-520B-43E5-B415-970328918330}"/>
   </bookViews>
   <sheets>
     <sheet name="ReceitaXDespesa" sheetId="3" r:id="rId1"/>
-    <sheet name="Exec_Por Grupo" sheetId="1" state="hidden" r:id="rId2"/>
-    <sheet name="Planilha1" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="Planilha2" sheetId="4" r:id="rId2"/>
+    <sheet name="Exec_Por Grupo" sheetId="1" state="hidden" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Planilha1!$A$1:$P$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">Planilha1!$A$1:$P$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="1" r:id="rId5"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -268,7 +272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -330,11 +334,122 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -419,6 +534,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2415,6 +2539,320 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Leopoldo Euler Marialva de Albuquerque" refreshedDate="46275.40976412037" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="53" xr:uid="{96A2F22B-9851-447E-BF55-32AFFD6526E0}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:C1048576" sheet="ReceitaXDespesa"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="Mês/Ano" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-01-01T00:00:00" maxDate="2026-12-02T00:00:00"/>
+    </cacheField>
+    <cacheField name="Item Orçamentário" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Valor" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-91.791328169999986" maxValue="154.63542719999998"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="53">
+  <r>
+    <d v="2026-01-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-01-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <n v="62.844099030000002"/>
+  </r>
+  <r>
+    <d v="2026-01-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <n v="154.63542719999998"/>
+  </r>
+  <r>
+    <d v="2026-01-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="-91.791328169999986"/>
+  </r>
+  <r>
+    <d v="2026-02-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-02-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <n v="71.107409860000004"/>
+  </r>
+  <r>
+    <d v="2026-02-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <n v="65.867006619999998"/>
+  </r>
+  <r>
+    <d v="2026-02-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="5.2404032400000062"/>
+  </r>
+  <r>
+    <d v="2026-03-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-03-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <n v="75.044984989999989"/>
+  </r>
+  <r>
+    <d v="2026-03-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <n v="54.581181280000003"/>
+  </r>
+  <r>
+    <d v="2026-03-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="20.463803709999986"/>
+  </r>
+  <r>
+    <d v="2026-04-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-04-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <n v="91.82818374"/>
+  </r>
+  <r>
+    <d v="2026-04-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <n v="41.371067400000001"/>
+  </r>
+  <r>
+    <d v="2026-04-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="50.457116339999999"/>
+  </r>
+  <r>
+    <d v="2026-05-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-05-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <n v="77.415932499999997"/>
+  </r>
+  <r>
+    <d v="2026-05-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <n v="80.184171169999999"/>
+  </r>
+  <r>
+    <d v="2026-05-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="-2.7682386700000023"/>
+  </r>
+  <r>
+    <d v="2026-06-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-06-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <n v="75.166762640000002"/>
+  </r>
+  <r>
+    <d v="2026-06-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <n v="92.382151069999992"/>
+  </r>
+  <r>
+    <d v="2026-06-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="-17.21538842999999"/>
+  </r>
+  <r>
+    <d v="2026-07-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-07-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <n v="70.888043189999991"/>
+  </r>
+  <r>
+    <d v="2026-07-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <n v="99.462564389999997"/>
+  </r>
+  <r>
+    <d v="2026-07-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="-28.574521200000007"/>
+  </r>
+  <r>
+    <d v="2026-08-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-08-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <n v="76.738591329999991"/>
+  </r>
+  <r>
+    <d v="2026-08-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <n v="77.35292192"/>
+  </r>
+  <r>
+    <d v="2026-08-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="-0.61433059000000867"/>
+  </r>
+  <r>
+    <d v="2026-09-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-09-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-09-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-09-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <d v="2026-10-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-10-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-10-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-10-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <d v="2026-11-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-11-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-11-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-11-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <d v="2026-12-01T00:00:00"/>
+    <s v="LOA (A)"/>
+    <n v="84.4166666666667"/>
+  </r>
+  <r>
+    <d v="2026-12-01T00:00:00"/>
+    <s v="Receita Arrecadada (B)"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-12-01T00:00:00"/>
+    <s v="Despesa Realizada (C)"/>
+    <m/>
+  </r>
+  <r>
+    <d v="2026-12-01T00:00:00"/>
+    <s v="Saldo (B-C)"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5606F569-D500-4B4F-95B4-2EACD5DAD170}" name="Tabela dinâmica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:C18" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="3">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -3303,6 +3741,106 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7906E5-5AAB-4F02-B6BE-5DAC634E0134}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="34"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="37"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="35"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="37"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="35"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="35"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="37"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="35"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="37"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="37"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="37"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="35"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="37"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="35"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="37"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="35"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="37"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="38"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F53F72-D795-49FC-9398-FBDE53A0A7F9}">
   <dimension ref="B3:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3430,7 +3968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAC02C4-A2C3-4869-A45C-FC4CAB74D8EC}">
   <dimension ref="A2:U59"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
